--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>136597743</v>
       </c>
       <c r="B7" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136596434</v>
       </c>
       <c r="B10" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>136594266</v>
       </c>
       <c r="B25" t="n">
-        <v>92513</v>
+        <v>92516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>136596751</v>
       </c>
       <c r="B30" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136594273</v>
       </c>
       <c r="B41" t="n">
-        <v>92780</v>
+        <v>92783</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136592428</v>
       </c>
       <c r="B43" t="n">
-        <v>110361</v>
+        <v>110364</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1576,7 +1576,7 @@
         <v>136596434</v>
       </c>
       <c r="B10" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>136594266</v>
       </c>
       <c r="B25" t="n">
-        <v>92516</v>
+        <v>92517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136594273</v>
       </c>
       <c r="B41" t="n">
-        <v>92783</v>
+        <v>92784</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136592428</v>
       </c>
       <c r="B43" t="n">
-        <v>110364</v>
+        <v>110365</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>136597743</v>
       </c>
       <c r="B7" t="n">
-        <v>91641</v>
+        <v>91643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136596434</v>
       </c>
       <c r="B10" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>136594266</v>
       </c>
       <c r="B25" t="n">
-        <v>92517</v>
+        <v>92522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>136596751</v>
       </c>
       <c r="B30" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136594273</v>
       </c>
       <c r="B41" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136592428</v>
       </c>
       <c r="B43" t="n">
-        <v>110365</v>
+        <v>110370</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>136597743</v>
       </c>
       <c r="B7" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136596434</v>
       </c>
       <c r="B10" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>136594266</v>
       </c>
       <c r="B25" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>136596751</v>
       </c>
       <c r="B30" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>136594273</v>
       </c>
       <c r="B41" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>136592428</v>
       </c>
       <c r="B43" t="n">
-        <v>110370</v>
+        <v>110372</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ44"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,7 +1255,7 @@
         <v>136597743</v>
       </c>
       <c r="B7" t="n">
-        <v>91645</v>
+        <v>91647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,48 +1354,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112275250</v>
+        <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>92134</v>
+        <v>88607</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1106</v>
+        <v>1008</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Naturskoleskogen, Srm</t>
+          <t>Larslund, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646166</v>
+        <v>646626</v>
       </c>
       <c r="R8" t="n">
-        <v>6568529</v>
+        <v>6568939</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,46 +1435,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112275250</t>
+          <t>https://artportalen.se/Sighting/137023259</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121241213</v>
+        <v>112275250</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>92134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,37 +1467,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Larslund, Srm</t>
+          <t>Naturskoleskogen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646322</v>
+        <v>646166</v>
       </c>
       <c r="R9" t="n">
-        <v>6568869</v>
+        <v>6568529</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,12 +1521,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,31 +1537,46 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121241213</t>
+          <t>https://artportalen.se/Sighting/112275250</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136596434</v>
+        <v>121241213</v>
       </c>
       <c r="B10" t="n">
-        <v>92113</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646488</v>
+        <v>646322</v>
       </c>
       <c r="R10" t="n">
-        <v>6568966</v>
+        <v>6568869</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1669,63 +1669,54 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136596434</t>
+          <t>https://artportalen.se/Sighting/121241213</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16596581</v>
+        <v>136596434</v>
       </c>
       <c r="B11" t="n">
-        <v>92564</v>
+        <v>92115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Larslund strax N om, Srm</t>
+          <t>Larslund, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646434</v>
+        <v>646488</v>
       </c>
       <c r="R11" t="n">
-        <v>6568901</v>
+        <v>6568966</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,12 +1740,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,43 +1756,28 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16596581</t>
+          <t>https://artportalen.se/Sighting/136596434</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73563665</v>
+        <v>16596581</v>
       </c>
       <c r="B12" t="n">
         <v>92564</v>
@@ -1829,19 +1805,26 @@
           <t>(Fr.) Donk</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Naturskoleskogen, Srm</t>
+          <t>Larslund strax N om, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646207</v>
+        <v>646434</v>
       </c>
       <c r="R12" t="n">
-        <v>6568477</v>
+        <v>6568901</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1868,12 +1851,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2018-10-13</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2018-10-13</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,84 +1865,85 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>gran</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73563665</t>
+          <t>https://artportalen.se/Sighting/16596581</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16596147</v>
+        <v>73563665</v>
       </c>
       <c r="B13" t="n">
-        <v>93231</v>
+        <v>92564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1968</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Larslund, 100 m NO om, Srm</t>
+          <t>Naturskoleskogen, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>646541</v>
+        <v>646207</v>
       </c>
       <c r="R13" t="n">
-        <v>6568943</v>
+        <v>6568477</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1986,12 +1970,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2018-10-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2018-10-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,73 +1984,84 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>gammal tallskog</t>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16596147</t>
+          <t>https://artportalen.se/Sighting/73563665</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16596558</v>
+        <v>16596147</v>
       </c>
       <c r="B14" t="n">
-        <v>96708</v>
+        <v>93231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>1968</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Larslund 150 m N om, Srm</t>
+          <t>Larslund, 100 m NO om, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>646474</v>
+        <v>646541</v>
       </c>
       <c r="R14" t="n">
-        <v>6568986</v>
+        <v>6568943</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2112,7 +2107,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>gammal barrskog</t>
+          <t>gammal tallskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2129,16 +2124,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16596558</t>
+          <t>https://artportalen.se/Sighting/16596147</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121237954</v>
+        <v>16596558</v>
       </c>
       <c r="B15" t="n">
-        <v>92497</v>
+        <v>96708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,37 +2141,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3884</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandsborg, Srm</t>
+          <t>Larslund 150 m N om, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>646130</v>
+        <v>646474</v>
       </c>
       <c r="R15" t="n">
-        <v>6568421</v>
+        <v>6568986</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2200,12 +2195,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2216,78 +2211,74 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>gammal barrskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121237954</t>
+          <t>https://artportalen.se/Sighting/16596558</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16596570</v>
+        <v>121237954</v>
       </c>
       <c r="B16" t="n">
-        <v>93189</v>
+        <v>92497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>3884</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Larslund 150 m N om, Srm</t>
+          <t>Sandsborg, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>646460</v>
+        <v>646130</v>
       </c>
       <c r="R16" t="n">
-        <v>6568951</v>
+        <v>6568421</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2311,12 +2302,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2327,36 +2318,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16596570</t>
+          <t>https://artportalen.se/Sighting/121237954</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16596269</v>
+        <v>16596570</v>
       </c>
       <c r="B17" t="n">
-        <v>93209</v>
+        <v>93189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2364,34 +2350,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Larslund, 200 m SV om, Srm</t>
+          <t>Larslund 150 m N om, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>646346</v>
+        <v>646460</v>
       </c>
       <c r="R17" t="n">
-        <v>6568796</v>
+        <v>6568951</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2437,7 +2432,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2454,13 +2449,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16596269</t>
+          <t>https://artportalen.se/Sighting/16596570</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16693358</v>
+        <v>16596269</v>
       </c>
       <c r="B18" t="n">
         <v>93209</v>
@@ -2491,14 +2486,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Naturskolan, V om Kiholm, Srm</t>
+          <t>Larslund, 200 m SV om, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>646255</v>
+        <v>646346</v>
       </c>
       <c r="R18" t="n">
-        <v>6568522</v>
+        <v>6568796</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2525,12 +2520,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2544,7 +2539,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>blandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2561,13 +2556,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16693358</t>
+          <t>https://artportalen.se/Sighting/16596269</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16693727</v>
+        <v>16693358</v>
       </c>
       <c r="B19" t="n">
         <v>93209</v>
@@ -2598,17 +2593,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Larslund, 150 m NNO om, Srm</t>
+          <t>Naturskolan, V om Kiholm, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>646495</v>
+        <v>646255</v>
       </c>
       <c r="R19" t="n">
-        <v>6568996</v>
+        <v>6568522</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2651,7 +2646,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>mossrik barrskog</t>
+          <t>blandskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2668,16 +2663,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16693727</t>
+          <t>https://artportalen.se/Sighting/16693358</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16596560</v>
+        <v>16693727</v>
       </c>
       <c r="B20" t="n">
-        <v>93215</v>
+        <v>93209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2685,37 +2680,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Larslund 150 m N om, Srm</t>
+          <t>Larslund, 150 m NNO om, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>646448</v>
+        <v>646495</v>
       </c>
       <c r="R20" t="n">
-        <v>6568968</v>
+        <v>6568996</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2739,12 +2734,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2758,7 +2753,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>gammal barrskog</t>
+          <t>mossrik barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2775,16 +2770,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16596560</t>
+          <t>https://artportalen.se/Sighting/16693727</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112275279</v>
+        <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93215</v>
+        <v>93425</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2792,40 +2787,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Naturskoleskogen, Srm</t>
+          <t>Larslund, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>646126</v>
+        <v>646600</v>
       </c>
       <c r="R21" t="n">
-        <v>6568636</v>
+        <v>6568941</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2849,12 +2841,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,77 +2855,71 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112275279</t>
+          <t>https://artportalen.se/Sighting/137023037</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128579897</v>
+        <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>89085</v>
+        <v>93425</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4379</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lina vid Naturskolan, Srm</t>
+          <t>Larslund, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>646307</v>
+        <v>646626</v>
       </c>
       <c r="R22" t="n">
-        <v>6568454</v>
+        <v>6568939</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2957,12 +2943,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2973,74 +2959,69 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128579897</t>
+          <t>https://artportalen.se/Sighting/137023208</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104721941</v>
+        <v>16596560</v>
       </c>
       <c r="B23" t="n">
-        <v>89143</v>
+        <v>93215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4405</v>
+        <v>4368</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Södertälje naturskola, strax V om, Srm</t>
+          <t>Larslund 150 m N om, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>646196</v>
+        <v>646448</v>
       </c>
       <c r="R23" t="n">
-        <v>6568413</v>
+        <v>6568968</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3064,12 +3045,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3083,7 +3064,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3100,16 +3081,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104721941</t>
+          <t>https://artportalen.se/Sighting/16596560</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>16693067</v>
+        <v>112275279</v>
       </c>
       <c r="B24" t="n">
-        <v>92841</v>
+        <v>93215</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3117,34 +3098,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4745</v>
+        <v>4368</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>V om Kiholm, 350 m NV om Södertälje naturskola, Srm</t>
+          <t>Naturskoleskogen, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>646148</v>
+        <v>646126</v>
       </c>
       <c r="R24" t="n">
-        <v>6568776</v>
+        <v>6568636</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3171,12 +3155,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3185,12 +3169,13 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>hällmarkstallskog</t>
+          <t>äldre barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3207,16 +3192,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16693067</t>
+          <t>https://artportalen.se/Sighting/112275279</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136594266</v>
+        <v>128579897</v>
       </c>
       <c r="B25" t="n">
-        <v>92524</v>
+        <v>89085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3224,37 +3209,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5420</v>
+        <v>4379</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södertälje Naturskola, Srm</t>
+          <t>Lina vid Naturskolan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>646330</v>
+        <v>646307</v>
       </c>
       <c r="R25" t="n">
-        <v>6568813</v>
+        <v>6568454</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3278,12 +3263,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3294,69 +3279,74 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136594266</t>
+          <t>https://artportalen.se/Sighting/128579897</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112275263</v>
+        <v>104721941</v>
       </c>
       <c r="B26" t="n">
-        <v>93223</v>
+        <v>89143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5448</v>
+        <v>4405</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Naturskoleskogen, Srm</t>
+          <t>Södertälje naturskola, strax V om, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>646200</v>
+        <v>646196</v>
       </c>
       <c r="R26" t="n">
-        <v>6568598</v>
+        <v>6568413</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3380,12 +3370,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3416,16 +3406,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112275263</t>
+          <t>https://artportalen.se/Sighting/104721941</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>16596577</v>
+        <v>16693067</v>
       </c>
       <c r="B27" t="n">
-        <v>91409</v>
+        <v>92841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3433,34 +3423,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5741</v>
+        <v>4745</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Larslund strax N om, Srm</t>
+          <t>V om Kiholm, 350 m NV om Södertälje naturskola, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>646434</v>
+        <v>646148</v>
       </c>
       <c r="R27" t="n">
-        <v>6568901</v>
+        <v>6568776</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3487,12 +3477,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3506,7 +3496,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>gammal barrskog</t>
+          <t>hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3523,54 +3513,54 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16596577</t>
+          <t>https://artportalen.se/Sighting/16693067</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16693675</v>
+        <v>136594266</v>
       </c>
       <c r="B28" t="n">
-        <v>91409</v>
+        <v>92526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5741</v>
+        <v>5420</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>V om Kiholm, 250 m NNO om Naturskolan, Srm</t>
+          <t>Södertälje Naturskola, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>646388</v>
+        <v>646330</v>
       </c>
       <c r="R28" t="n">
-        <v>6568743</v>
+        <v>6568813</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3594,12 +3584,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3610,36 +3600,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16693675</t>
+          <t>https://artportalen.se/Sighting/136594266</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16693883</v>
+        <v>112275263</v>
       </c>
       <c r="B29" t="n">
-        <v>91409</v>
+        <v>93223</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3647,37 +3632,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5741</v>
+        <v>5448</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Larslund, 150 m NO - NNO om, Srm</t>
+          <t>Naturskoleskogen, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>646551</v>
+        <v>646200</v>
       </c>
       <c r="R29" t="n">
-        <v>6568956</v>
+        <v>6568598</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3701,12 +3686,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3720,7 +3705,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>mossrik barrskog</t>
+          <t>äldre barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3737,16 +3722,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16693883</t>
+          <t>https://artportalen.se/Sighting/112275263</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136596751</v>
+        <v>16596577</v>
       </c>
       <c r="B30" t="n">
-        <v>91628</v>
+        <v>91409</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3754,37 +3739,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5754</v>
+        <v>5741</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Larslund, Srm</t>
+          <t>Larslund strax N om, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>646568</v>
+        <v>646434</v>
       </c>
       <c r="R30" t="n">
-        <v>6568965</v>
+        <v>6568901</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3808,12 +3793,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3824,66 +3809,71 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>gammal barrskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136596751</t>
+          <t>https://artportalen.se/Sighting/16596577</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128579902</v>
+        <v>16693675</v>
       </c>
       <c r="B31" t="n">
-        <v>92928</v>
+        <v>91409</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5836</v>
+        <v>5741</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lina vid Naturskolan, Srm</t>
+          <t>V om Kiholm, 250 m NNO om Naturskolan, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>646307</v>
+        <v>646388</v>
       </c>
       <c r="R31" t="n">
-        <v>6568454</v>
+        <v>6568743</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3910,12 +3900,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3929,7 +3919,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>blandskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3946,16 +3936,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128579902</t>
+          <t>https://artportalen.se/Sighting/16693675</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16596333</v>
+        <v>16693883</v>
       </c>
       <c r="B32" t="n">
-        <v>93233</v>
+        <v>91409</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3963,34 +3953,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>5741</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Larslund, 200 m SV om, Srm</t>
+          <t>Larslund, 150 m NO - NNO om, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>646346</v>
+        <v>646551</v>
       </c>
       <c r="R32" t="n">
-        <v>6568796</v>
+        <v>6568956</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4017,12 +4007,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4031,13 +4021,12 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>mossrik barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4054,16 +4043,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16596333</t>
+          <t>https://artportalen.se/Sighting/16693883</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16596598</v>
+        <v>136596751</v>
       </c>
       <c r="B33" t="n">
-        <v>93233</v>
+        <v>91630</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4071,37 +4060,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Larslund 150 m N om, Srm</t>
+          <t>Larslund, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>646474</v>
+        <v>646568</v>
       </c>
       <c r="R33" t="n">
-        <v>6568986</v>
+        <v>6568965</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4125,12 +4114,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4139,74 +4128,68 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16596598</t>
+          <t>https://artportalen.se/Sighting/136596751</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16596615</v>
+        <v>128579902</v>
       </c>
       <c r="B34" t="n">
-        <v>93233</v>
+        <v>92928</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5964</v>
+        <v>5836</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Larslund strax N om, Srm</t>
+          <t>Lina vid Naturskolan, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>646434</v>
+        <v>646307</v>
       </c>
       <c r="R34" t="n">
-        <v>6568901</v>
+        <v>6568454</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4233,12 +4216,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4247,13 +4230,12 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>gammal barrskog</t>
+          <t>blandskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4270,54 +4252,54 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16596615</t>
+          <t>https://artportalen.se/Sighting/128579902</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16693754</v>
+        <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93233</v>
+        <v>93144</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>5836</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Larslund, 75 m NO om, Srm</t>
+          <t>Larslund, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>646502</v>
+        <v>646600</v>
       </c>
       <c r="R35" t="n">
-        <v>6568930</v>
+        <v>6568941</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4341,12 +4323,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4355,39 +4337,33 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>mossrik barrskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16693754</t>
+          <t>https://artportalen.se/Sighting/137023002</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>16596537</v>
+        <v>16596333</v>
       </c>
       <c r="B36" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4395,34 +4371,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Larslund 150 m N om, Srm</t>
+          <t>Larslund, 200 m SV om, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>646479</v>
+        <v>646346</v>
       </c>
       <c r="R36" t="n">
-        <v>6568999</v>
+        <v>6568796</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4463,12 +4439,13 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>bergig tallskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4485,16 +4462,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16596537</t>
+          <t>https://artportalen.se/Sighting/16596333</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>16692991</v>
+        <v>16596598</v>
       </c>
       <c r="B37" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4502,43 +4479,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>V om Kiholm, 250 m NV om Södertälje naturskola, Srm</t>
+          <t>Larslund 150 m N om, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>646137</v>
+        <v>646474</v>
       </c>
       <c r="R37" t="n">
-        <v>6568725</v>
+        <v>6568986</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4565,12 +4533,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4579,12 +4547,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Olikåldrig barrskog med björkinslag</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4601,16 +4570,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16692991</t>
+          <t>https://artportalen.se/Sighting/16596598</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>16693027</v>
+        <v>16596615</v>
       </c>
       <c r="B38" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4618,46 +4587,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>V om Kiholm, 550 m NNV om Södertälje naturskola, Srm</t>
+          <t>Larslund strax N om, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>646145</v>
+        <v>646434</v>
       </c>
       <c r="R38" t="n">
-        <v>6568972</v>
+        <v>6568901</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4676,17 +4636,17 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Ytterenhörna</t>
+          <t>Södertälje</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4695,12 +4655,13 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>bergig barrskog</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4717,16 +4678,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16693027</t>
+          <t>https://artportalen.se/Sighting/16596615</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>16693050</v>
+        <v>16693754</v>
       </c>
       <c r="B39" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4734,46 +4695,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>V om Kiholm, 350 m NV om Södertälje naturskola, Srm</t>
+          <t>Larslund, 75 m NO om, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>646148</v>
+        <v>646502</v>
       </c>
       <c r="R39" t="n">
-        <v>6568776</v>
+        <v>6568930</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4811,12 +4763,13 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>hällmarkstallskog</t>
+          <t>mossrik barrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4833,13 +4786,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16693050</t>
+          <t>https://artportalen.se/Sighting/16693754</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112275278</v>
+        <v>16596537</v>
       </c>
       <c r="B40" t="n">
         <v>93235</v>
@@ -4870,14 +4823,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Naturskoleskogen, Srm</t>
+          <t>Larslund 150 m N om, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>646126</v>
+        <v>646479</v>
       </c>
       <c r="R40" t="n">
-        <v>6568636</v>
+        <v>6568999</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4904,12 +4857,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4923,7 +4876,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
+          <t>bergig tallskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4940,54 +4893,63 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112275278</t>
+          <t>https://artportalen.se/Sighting/16596537</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136594273</v>
+        <v>16692991</v>
       </c>
       <c r="B41" t="n">
-        <v>92791</v>
+        <v>93235</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Södertälje Naturskola, Srm</t>
+          <t>V om Kiholm, 250 m NV om Södertälje naturskola, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>646330</v>
+        <v>646137</v>
       </c>
       <c r="R41" t="n">
-        <v>6568813</v>
+        <v>6568725</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5011,12 +4973,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5027,72 +4989,83 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Olikåldrig barrskog med björkinslag</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136594273</t>
+          <t>https://artportalen.se/Sighting/16692991</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>102014138</v>
+        <v>16693027</v>
       </c>
       <c r="B42" t="n">
-        <v>58817</v>
+        <v>93235</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>208249</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lina 12, Södertälje, Srm</t>
+          <t>V om Kiholm, 550 m NNV om Södertälje naturskola, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>646368</v>
+        <v>646145</v>
       </c>
       <c r="R42" t="n">
-        <v>6568735</v>
+        <v>6568972</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5111,32 +5084,17 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Södertälje</t>
+          <t>Ytterenhörna</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-07-02</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-07-02</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På stigen, gränsen mellan Underås och Dammkärr</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5147,31 +5105,36 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>bergig barrskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Sofie Frydenlund</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Sofie Frydenlund</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102014138</t>
+          <t>https://artportalen.se/Sighting/16693027</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136592428</v>
+        <v>16693050</v>
       </c>
       <c r="B43" t="n">
-        <v>110372</v>
+        <v>93235</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5179,41 +5142,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220320</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sandsborg, Srm</t>
+          <t>V om Kiholm, 350 m NV om Södertälje naturskola, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>646151</v>
+        <v>646148</v>
       </c>
       <c r="R43" t="n">
-        <v>6568391</v>
+        <v>6568776</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5237,12 +5205,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5253,75 +5221,71 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136592428</t>
+          <t>https://artportalen.se/Sighting/16693050</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>16693735</v>
+        <v>112275278</v>
       </c>
       <c r="B44" t="n">
-        <v>93200</v>
+        <v>93235</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003297</v>
+        <v>5966</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spricktaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum glaucopus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Larslund, 150 m NNO om, Srm</t>
+          <t>Naturskoleskogen, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>646495</v>
+        <v>646126</v>
       </c>
       <c r="R44" t="n">
-        <v>6568996</v>
+        <v>6568636</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5348,12 +5312,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5367,7 +5331,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>mossrik barrskog</t>
+          <t>äldre barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5383,6 +5347,450 @@
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112275278</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136594273</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92793</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Södertälje Naturskola, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>646330</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6568813</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Richard Vestin</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Richard Vestin</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136594273</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>102014138</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lina 12, Södertälje, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>646368</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6568735</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-07-02</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-07-02</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På stigen, gränsen mellan Underås och Dammkärr</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102014138</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136592428</v>
+      </c>
+      <c r="B47" t="n">
+        <v>110378</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sandsborg, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>646151</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6568391</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Richard Vestin</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Richard Vestin</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136592428</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>16693735</v>
+      </c>
+      <c r="B48" t="n">
+        <v>93200</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6003297</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spricktaggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hydnellum glaucopus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Larslund, 150 m NNO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>646495</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6568996</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>mossrik barrskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/16693735</t>
         </is>
@@ -5433,6 +5841,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>136597743</v>
       </c>
       <c r="B7" t="n">
-        <v>91647</v>
+        <v>91649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>88607</v>
+        <v>88609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>136596434</v>
       </c>
       <c r="B11" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136594266</v>
       </c>
       <c r="B28" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136596751</v>
       </c>
       <c r="B33" t="n">
-        <v>91630</v>
+        <v>91632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93144</v>
+        <v>93146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>136594273</v>
       </c>
       <c r="B45" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>136592428</v>
       </c>
       <c r="B47" t="n">
-        <v>110378</v>
+        <v>110380</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>136597743</v>
       </c>
       <c r="B7" t="n">
-        <v>91649</v>
+        <v>91650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>88609</v>
+        <v>88610</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>136596434</v>
       </c>
       <c r="B11" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136594266</v>
       </c>
       <c r="B28" t="n">
-        <v>92528</v>
+        <v>92529</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136596751</v>
       </c>
       <c r="B33" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93146</v>
+        <v>93147</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>136594273</v>
       </c>
       <c r="B45" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>136592428</v>
       </c>
       <c r="B47" t="n">
-        <v>110380</v>
+        <v>110381</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>136597743</v>
       </c>
       <c r="B7" t="n">
-        <v>91650</v>
+        <v>91656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>88610</v>
+        <v>88616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>136596434</v>
       </c>
       <c r="B11" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136594266</v>
       </c>
       <c r="B28" t="n">
-        <v>92529</v>
+        <v>92535</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136596751</v>
       </c>
       <c r="B33" t="n">
-        <v>91633</v>
+        <v>91639</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93147</v>
+        <v>93153</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>136594273</v>
       </c>
       <c r="B45" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>136592428</v>
       </c>
       <c r="B47" t="n">
-        <v>110381</v>
+        <v>110387</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>136597743</v>
       </c>
       <c r="B7" t="n">
-        <v>91656</v>
+        <v>91660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>88616</v>
+        <v>88620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>136596434</v>
       </c>
       <c r="B11" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>136594266</v>
       </c>
       <c r="B28" t="n">
-        <v>92535</v>
+        <v>92539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136596751</v>
       </c>
       <c r="B33" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93153</v>
+        <v>93157</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>136594273</v>
       </c>
       <c r="B45" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>136592428</v>
       </c>
       <c r="B47" t="n">
-        <v>110387</v>
+        <v>110391</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>88640</v>
+        <v>88650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93177</v>
+        <v>93187</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>88650</v>
+        <v>88651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93187</v>
+        <v>93188</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>88651</v>
+        <v>88654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93188</v>
+        <v>93191</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93191</v>
+        <v>93193</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>88654</v>
+        <v>88659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93193</v>
+        <v>93199</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>88659</v>
+        <v>88670</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93199</v>
+        <v>93211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>88670</v>
+        <v>88671</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93211</v>
+        <v>93212</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>88671</v>
+        <v>88674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93212</v>
+        <v>93215</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -1357,7 +1357,7 @@
         <v>137023259</v>
       </c>
       <c r="B8" t="n">
-        <v>88674</v>
+        <v>88678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>137023037</v>
       </c>
       <c r="B21" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>137023208</v>
       </c>
       <c r="B22" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>137023002</v>
       </c>
       <c r="B35" t="n">
-        <v>93215</v>
+        <v>93219</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
